--- a/docs/萝卜地牢开发文档/NPC总表.xlsx
+++ b/docs/萝卜地牢开发文档/NPC总表.xlsx
@@ -1459,295 +1459,212 @@
       </c>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>N03</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>owo</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Owo</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>一个看上去很容易自由落体的生物。</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>(它只是闪了一下手电筒)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>纯对话（闪一下手电筒）</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>0 层</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>0 层四角（NW/NE/SW/SE）随机 4 名之一；候选池 = 船/owo/雷暴/海滨/桃井/月华，互不重复</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>sprites/OwoSprite.java  ·  帧 32-47</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>idle 2 段 + die/operate 帧</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>sprites/OwoSprite.java  ·  帧 32-47（现成 16 帧，未接代码）</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>idle 2 段 + die/operate 帧；原类 Owo 已删除（0 层废弃）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>N04</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>电击雷暴</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>ThunderStorm</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>一颗电池形状的子弹，似乎不属于这个地牢。</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>我可以为你的子弹添加闪电链效果！
-嗯？...这里没有枪吗...
-...那这个给你好了。
-虽然比不上子弹，但这家伙硬度还可以。
-滋滋滋~</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>纯对话（自称能加闪电链，这层没枪，送电池状道具的台词）</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>0 层</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>0 层四角（NW/NE/SW/SE）随机 4 名之一；候选池 = 船/owo/雷暴/海滨/桃井/月华，互不重复</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>sprites/ThunderStormSprite.java  ·  帧 48-63</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>台词有 msg0..3 + loop</t>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>sprites/ThunderStormSprite.java  ·  帧 48-63（现成 16 帧，未接代码）</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>台词有 msg0..3 + loop；原类 ThunderStorm 已删除（0 层废弃）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>N05</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>船</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Boat</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>千年的金牌骇客，她似乎专心在听着什么……</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>我会和你保持联络，以及米斯特船只不过是个权限狗罢了。</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>纯对话（千年的金牌骇客）</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>0 层</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>0 层四角（NW/NE/SW/SE）随机 4 名之一；候选池 = 船/owo/雷暴/海滨/桃井/月华，互不重复</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>sprites/BoatSprite.java  ·  帧 64-79</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>有 20 帧 idle</t>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>sprites/BoatSprite.java  ·  帧 64-79（现成 16 帧，未接代码）</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>有 20 帧 idle；原类 Boat 已删除（0 层废弃）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>N06</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>海滨</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>SeaShore</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>一个畏缩的研究者，看起来像是在研究什么黑魔法，还是离他远一点为好。</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>（指点江山..指点江山...指点江山....）
-什么？！是虫子？叫鸡治？
-嘿嘿...祝福极速毒粹药...嘿嘿...
-嘿嘿...匿踪斗篷疾行者...嘿嘿...
-嘿嘿...术士百暴凝血刃...嘿嘿...</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>纯对话（研究黑魔法，随机念叨）</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>0 层</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>0 层四角（NW/NE/SW/SE）随机 4 名之一；候选池 = 船/owo/雷暴/海滨/桃井/月华，互不重复</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>sprites/SeaShoreSprite.java  ·  帧 80-95</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>台词有 msg0/msg1 + loop0..2</t>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>sprites/SeaShoreSprite.java  ·  帧 80-95（现成 16 帧，未接代码）</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>台词有 msg0/msg1 + loop0..2；原类 SeaShore 已删除（0 层废弃）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>N07</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>桃井</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>PW</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>~~~</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>~~~</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>纯对话（文本目前是 ~~~ 占位）</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>0 层</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>0 层四角（NW/NE/SW/SE）随机 4 名之一；候选池 = 船/owo/雷暴/海滨/桃井/月华，互不重复</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>sprites/PWSprite.java  ·  帧 96-111</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>文本未写，需要补</t>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>sprites/PWSprite.java  ·  帧 96-111（现成 16 帧，未接代码）</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>文本未写，需要补；原类 PW 已删除（0 层废弃）</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1704,12 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>0 层（1 层也有）</t>
+          <t>1 层</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>0 层四角（NW/NE/SW/SE）随机 4 名之一；候选池 = 船/owo/雷暴/海滨/桃井/月华，互不重复；另外 1 层固定在入口前一格</t>
+          <t>SewerLevel.createMobs()（1 层）</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1802,12 +1719,12 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>sprites/MoonLightSprite.java  ·  帧 112-127</t>
+          <t>sprites/MoonLightSprite.java + actors/mobs/npcs/MoonLight.java  ·  帧 112-127</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>另有 the_catist 变体文本，另有 0 层/1 层两处生成</t>
+          <t>另有 the_catist 变体文本；1 层入口前一格生成（原 0 层那份随 ZeroLevel 一起删了）</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2617,77 +2534,89 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>“已实现”= 游戏里已经能刷出来、有对应类；“未实现”= 图在素材里但没接代码。橙色底的就是未实现的。</t>
+          <t>“已实现”= 有 NPC 类 + Sprite 类，且在某个 Level 里真的会被生成；“未实现”= 图在素材里但没接代码。橙色底的就是未实现的。状态和出没层都是从代码里现扫的，删/加类之后重跑 build 会自动更新。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>帧索引</t>
+          <t>第 0 层</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>new_npc.png 是 16×16 一帧、每行 16 帧。第 r 行第 c 列的帧号 = r*16+c，写 Sprite 类时 idle.frames(frames, ...) 直接用这个号。</t>
+          <t>已废弃并删除：ZeroLevel 不再注册进主线分支，0 层那批 NPC（船/owo/雷暴/海滨/桃井）的类、贴图类与文本一并删掉，月华保留（1 层还在用）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>中文名 / 英文名 / 描述 / 对话</t>
+          <t>帧索引</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>对应 properties：name / desc / msg*。多个数字后缀的 msg0、msg1 就是交互时按顺序说的话。</t>
+          <t>new_npc.png 是 16×16 一帧、每行 16 帧。第 r 行第 c 列的帧号 = r*16+c，写 Sprite 类时 idle.frames(frames, ...) 直接用这个号。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>中文名 / 英文名 / 描述 / 对话</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>这个 NPC 到底干什么：纯对话、买卖、任务、收费服务。想改成别的就在这里写清楚。</t>
+          <t>对应 properties：name / desc / msg*。多个数字后缀的 msg0、msg1 就是交互时按顺序说的话。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>出没层 / 刷新规则</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>现在是怎么刷的。想改（比如让游商去 2 层、改成必刷 3 个）也写这两列。</t>
+          <t>这个 NPC 到底干什么：纯对话、买卖、任务、收费服务。想改成别的就在这里写清楚。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>改完怎么给我</t>
+          <t>出没层 / 刷新规则</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>存盘后把文件发回来（或说“改好了，路径在 xxx”），我会用 tools/npc_table.py dump 把它读成 JSON，再逐行对照代码实现，不需要你再打一遍字。</t>
+          <t>现在是怎么刷的。想改（比如让游商去 2 层、改成必刷 3 个）也写这两列。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>改完怎么给我</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>存盘后把文件发回来（或说“改好了，路径在 xxx”），我会用 tools/npc_table.py dump 把它读成 JSON，再逐行对照代码实现，不需要你再打一遍字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
           <t>注意</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>第 10、12 行我标了“（续帧？）”：它们的帧和上一行风格一致但像素不相同，需要你确认是同一角色的第二段动画，还是两个独立角色——这个我判断不了。</t>
         </is>
